--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC124CA-DA72-49C5-B6D1-5D1C3138284F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FA6F1B-3439-414B-A862-087870AC47A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -48,22 +48,22 @@
     <t>Title__c</t>
   </si>
   <si>
+    <t>RIFANSTitle__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Automation Test Description</t>
+  </si>
+  <si>
     <t>Automation Focus Area Regression</t>
   </si>
   <si>
-    <t>RIFANSTitle__c</t>
-  </si>
-  <si>
-    <t>AFAR</t>
-  </si>
-  <si>
-    <t>Description__c</t>
-  </si>
-  <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Automation Test Description</t>
+    <t>FREG</t>
   </si>
 </sst>
 </file>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -455,10 +455,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -488,13 +488,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FA6F1B-3439-414B-A862-087870AC47A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA355FA6-B99E-4F28-BF63-F85441F7F2AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Edition" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -421,14 +422,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0685D0A-1C62-4493-962F-E9089FACC420}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -448,17 +449,6 @@
       </c>
       <c r="C2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -467,15 +457,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CB241-7228-4982-9E64-6A9F8CB74DE4}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC41801-C055-489A-8146-D441E112168C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>

--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA355FA6-B99E-4F28-BF63-F85441F7F2AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C03C039-6428-4846-9511-B5FAFC3606DE}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -61,10 +61,10 @@
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>Automation Focus Area Regression</t>
-  </si>
-  <si>
     <t>FREG</t>
+  </si>
+  <si>
+    <t>Automation Focus Area</t>
   </si>
 </sst>
 </file>
@@ -423,13 +423,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0685D0A-1C62-4493-962F-E9089FACC420}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -448,7 +448,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -459,9 +459,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CB241-7228-4982-9E64-6A9F8CB74DE4}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -469,7 +469,7 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -480,13 +480,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC41801-C055-489A-8146-D441E112168C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>

--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C03C039-6428-4846-9511-B5FAFC3606DE}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC46AD2B-F9A3-492F-A3CA-CB4920A92B3C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>FREG</t>
   </si>
   <si>
-    <t>Automation Focus Area</t>
+    <t>Execution Focus Area for Automation</t>
   </si>
 </sst>
 </file>
@@ -423,13 +423,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0685D0A-1C62-4493-962F-E9089FACC420}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -449,6 +449,28 @@
       </c>
       <c r="C2" t="s">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CB241-7228-4982-9E64-6A9F8CB74DE4}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -456,37 +478,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CB241-7228-4982-9E64-6A9F8CB74DE4}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC41801-C055-489A-8146-D441E112168C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>

--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC46AD2B-F9A3-492F-A3CA-CB4920A92B3C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE7AFB4-6678-449D-847E-AFB0DDCE9D17}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>FREG</t>
   </si>
   <si>
-    <t>Execution Focus Area for Automation</t>
+    <t xml:space="preserve">Permanent Focus Area for Automation </t>
   </si>
 </sst>
 </file>
@@ -423,13 +423,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0685D0A-1C62-4493-962F-E9089FACC420}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -460,9 +460,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CB241-7228-4982-9E64-6A9F8CB74DE4}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -481,13 +481,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC41801-C055-489A-8146-D441E112168C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>

--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE7AFB4-6678-449D-847E-AFB0DDCE9D17}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D312B723-9784-430C-AEB1-F032366B412A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>FREG</t>
   </si>
   <si>
-    <t xml:space="preserve">Permanent Focus Area for Automation </t>
+    <t>Automation Execution Focus Area</t>
   </si>
 </sst>
 </file>
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -108,6 +108,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,13 +424,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0685D0A-1C62-4493-962F-E9089FACC420}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,14 +441,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -460,9 +461,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CB241-7228-4982-9E64-6A9F8CB74DE4}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -481,13 +482,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC41801-C055-489A-8146-D441E112168C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>

--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D312B723-9784-430C-AEB1-F032366B412A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECB8E02-6F3D-4234-B2AA-24DABD088DC2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -424,13 +424,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0685D0A-1C62-4493-962F-E9089FACC420}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,7 +441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -461,9 +461,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450CB241-7228-4982-9E64-6A9F8CB74DE4}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -482,13 +482,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC41801-C055-489A-8146-D441E112168C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>

--- a/src/main/resources/FocusArea_Field_Values.xlsx
+++ b/src/main/resources/FocusArea_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECB8E02-6F3D-4234-B2AA-24DABD088DC2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9B8A38-F06A-4847-82D3-A7AFCDAC58CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{33FB0DD0-3C34-4541-BB0D-269950BE7E57}"/>
   </bookViews>
